--- a/output/pdf_financials_xlsx/QSP.UN.xlsx
+++ b/output/pdf_financials_xlsx/QSP.UN.xlsx
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -4601,7 +4601,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>-500</v>
       </c>
